--- a/camp_registration_forms/011_outdoor_education_camp_registration_form--camp_registration_forms.xlsx
+++ b/camp_registration_forms/011_outdoor_education_camp_registration_form--camp_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'summer'}</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Summer'}</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'winter'}</t>
+          <t>winter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Winter'}</t>
+          <t>Winter</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'week'}</t>
+          <t>week</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Week'}</t>
+          <t>Week</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'two_weeks'}</t>
+          <t>two_weeks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Two Weeks'}</t>
+          <t>Two Weeks</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'three_weeks'}</t>
+          <t>three_weeks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Three Weeks'}</t>
+          <t>Three Weeks</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'four_weeks'}</t>
+          <t>four_weeks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Four Weeks'}</t>
+          <t>Four Weeks</t>
         </is>
       </c>
     </row>
